--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_s_2020_los_lagos.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_s_2020_los_lagos.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:46</t>
+    <t xml:space="preserve">2026-10-05 02:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>272275.38</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>325846.62</v>
+        <v>325846.63</v>
       </c>
     </row>
     <row r="4">
@@ -535,7 +535,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>282407.62</v>
+        <v>282407.63</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>323283.69</v>
@@ -557,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>291723.62</v>
+        <v>291723.63</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>337883.34</v>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>333367.62</v>
+        <v>333367.63</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>389873.41</v>
